--- a/data/datasets/test_reports/PCRTA/PCRTA_of_feature_group_3.xlsx
+++ b/data/datasets/test_reports/PCRTA/PCRTA_of_feature_group_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>conditional_relevance_for_gamma</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>conditional_relevance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -475,16 +480,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.557801464288513</v>
+        <v>1.55780160745715</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8452344558930062</v>
+        <v>-0.8452348827282556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02932605545773892</v>
+        <v>0.02932604387170823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.512255678478439</v>
+        <v>0.5122557685058289</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -492,6 +497,11 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -507,16 +517,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1727613707230485</v>
+        <v>0.1727615792345244</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.061296237643939</v>
+        <v>-3.061297190439081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2756156813758274</v>
+        <v>0.275615631319696</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8286795734682859</v>
+        <v>0.8286796538188861</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -524,6 +534,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -539,16 +554,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.6733851823012523</v>
+        <v>-0.6733851004372881</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1002978742251435</v>
+        <v>0.1002978410425776</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4751478259177714</v>
+        <v>0.4751478078444276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2930622078444944</v>
+        <v>0.2930622158528459</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -556,6 +571,11 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -571,16 +591,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7371815387494239</v>
+        <v>0.7371814865829986</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1619854640545648</v>
+        <v>-0.1619843723954738</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1482625261784143</v>
+        <v>0.1482625367595531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3564240576509121</v>
+        <v>0.356423795139144</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -588,6 +608,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -603,16 +628,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1952301073751221</v>
+        <v>0.1952299917930404</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1431445871048286</v>
+        <v>0.1431447902275348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2702277236159435</v>
+        <v>0.2702277513001512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2827349320278906</v>
+        <v>0.2827348831416636</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -620,6 +645,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -635,16 +665,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.03618013154102207</v>
+        <v>-0.03618013345065625</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1423729294263439</v>
+        <v>0.1423728379029823</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3260640941976306</v>
+        <v>0.3260640946595569</v>
       </c>
       <c r="F7" t="n">
-        <v>0.282920654989204</v>
+        <v>0.2829206770177448</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -652,6 +682,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -667,16 +702,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.294807183013703</v>
+        <v>-2.29480686166425</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.001104850868151574</v>
+        <v>-0.001105176210133306</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7508946196779152</v>
+        <v>0.7508945809795752</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3175778494007785</v>
+        <v>0.3175779281239897</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -684,6 +719,11 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -699,16 +739,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.975178243229961</v>
+        <v>-1.975178253050079</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.445170930195476</v>
+        <v>-1.445170697795919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7095402659064882</v>
+        <v>0.7095402672679203</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6273249745866067</v>
+        <v>0.6273249345785332</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -716,6 +756,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -731,16 +776,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2113287899821561</v>
+        <v>0.2113287615325083</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6600375441797215</v>
+        <v>0.6600375897850672</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2663752142304789</v>
+        <v>0.2663752210323819</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1642271733929377</v>
+        <v>0.164227163774588</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -748,6 +793,11 @@
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -763,16 +813,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1.045125565431333</v>
+        <v>-1.045125389629274</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.318087076848041</v>
+        <v>-2.31808759359454</v>
       </c>
       <c r="E11" t="n">
-        <v>0.553181907368948</v>
+        <v>0.5531818724847628</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753683455234965</v>
+        <v>0.7536835168151015</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -780,6 +830,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -795,16 +850,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.488966973069711</v>
+        <v>-2.488966967854402</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1001413881394516</v>
+        <v>0.100141555230854</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7732780982714547</v>
+        <v>0.7732780976964181</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2930999746872223</v>
+        <v>0.293099934360693</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -812,6 +867,11 @@
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
@@ -827,16 +887,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-2.398382823783736</v>
+        <v>-2.398380974505407</v>
       </c>
       <c r="D13" t="n">
-        <v>1.781104559532931</v>
+        <v>1.781104292024127</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7630806336956323</v>
+        <v>0.7630804211856771</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01483119889908513</v>
+        <v>0.01483121226304607</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -844,6 +904,11 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
@@ -859,16 +924,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1.589030061015773</v>
+        <v>-1.589029292356296</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8406197371640601</v>
+        <v>-0.840619833887933</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6514128599473744</v>
+        <v>0.6514127348449377</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5112817093172495</v>
+        <v>0.5112817297449186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -876,6 +941,11 @@
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
